--- a/activity_browser/templates/scenarios/parameter-scenarios.xlsx
+++ b/activity_browser/templates/scenarios/parameter-scenarios.xlsx
@@ -636,7 +636,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>- Rows or columns whose first cell / header starts with # are ignored when Activity Browser loads the file. Use # to leave notes in the file.</t>
+          <t>- Comment rows: start the row with # (ignored on import). Comment columns: name them with a leading _ (e.g. _notes).</t>
         </is>
       </c>
     </row>
